--- a/tabular/reference/ervr/ervr_data.xlsx
+++ b/tabular/reference/ervr/ervr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF530490-6141-A046-B9CA-357EA67E0604}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6C8BFA-70F6-5546-8586-974378E8A297}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="860" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1240" yWindow="520" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="137">
   <si>
     <t>sequenceID</t>
   </si>
@@ -251,9 +251,6 @@
     <t>ERV-3.Lambda.52</t>
   </si>
   <si>
-    <t>ERV-3.Lambda.57</t>
-  </si>
-  <si>
     <t>ERV-3.Lambda.40</t>
   </si>
   <si>
@@ -263,21 +260,12 @@
     <t>ERV-3.Lambda.74</t>
   </si>
   <si>
-    <t>ERV-1.Rho.Rb.31</t>
-  </si>
-  <si>
-    <t>ERV-1.Rho.Rb.39</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta.HF.52A</t>
   </si>
   <si>
     <t>ERV-1.Zeta.19</t>
   </si>
   <si>
-    <t>ERV-1.Zeta.35</t>
-  </si>
-  <si>
     <t>medium reiteration frequency repeat 101</t>
   </si>
   <si>
@@ -359,9 +347,6 @@
     <t>lineage_id</t>
   </si>
   <si>
-    <t>Unclassified</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta.W9P.P</t>
   </si>
   <si>
@@ -371,33 +356,9 @@
     <t>HF</t>
   </si>
   <si>
-    <t>ERVR-1.Zeta.MER41</t>
-  </si>
-  <si>
-    <t>ERVR-1.Zeta.MER57</t>
-  </si>
-  <si>
-    <t>Rhoretrovirus</t>
-  </si>
-  <si>
     <t>ERVR-1.Theta.LOR1</t>
   </si>
   <si>
-    <t>ERVR-1.Theta.37</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.43</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.38</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.MER31</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.MER21</t>
-  </si>
-  <si>
     <t>ERVR-1.Zeta.MER83A</t>
   </si>
   <si>
@@ -419,36 +380,12 @@
     <t>excluded</t>
   </si>
   <si>
-    <t>ERVR-1.Theta.101</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.MER61</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.MER89</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.MER34b</t>
-  </si>
-  <si>
-    <t>ERVR-1.Unclassified.MER4</t>
-  </si>
-  <si>
-    <t>ERVR-1.Unclassified.MER4b</t>
-  </si>
-  <si>
-    <t>ERVR-1.Unclassified.MER65</t>
-  </si>
-  <si>
     <t>ERVR-3.Lambda.70</t>
   </si>
   <si>
     <t>ERVR-3.Lambda.76</t>
   </si>
   <si>
-    <t>ERVR-3.Lambda.16A3</t>
-  </si>
-  <si>
     <t>ERV-1.Eta.E.HQ</t>
   </si>
   <si>
@@ -465,6 +402,45 @@
   </si>
   <si>
     <t>NK</t>
+  </si>
+  <si>
+    <t>sublineage</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus L68</t>
+  </si>
+  <si>
+    <t>HERV-L68</t>
+  </si>
+  <si>
+    <t>ERV-3.Sigma.57</t>
+  </si>
+  <si>
+    <t>Sigmaretrovirus</t>
+  </si>
+  <si>
+    <t>endogenous retrovirus L47</t>
+  </si>
+  <si>
+    <t>ERV-L47</t>
+  </si>
+  <si>
+    <t>ERV-3.Sigma</t>
+  </si>
+  <si>
+    <t>ERV-3.Sigma.47</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.24.101</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.43</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.24.MER89</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda.16A3</t>
   </si>
 </sst>
 </file>
@@ -630,7 +606,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -843,6 +819,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8AD8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5FC79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39994506668294322"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF85FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1007,7 +1013,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1032,6 +1038,11 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1077,7 +1088,37 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1092,7 +1133,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF85FF"/>
       <color rgb="FFFF8AD8"/>
+      <color rgb="FFD5FC79"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1403,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1424,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>45</v>
@@ -1433,13 +1476,13 @@
         <v>46</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>1</v>
@@ -1475,42 +1518,42 @@
         <v>69</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>140</v>
+        <v>56</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>118</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2">
-        <v>6996</v>
+        <v>6896</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>35</v>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>2</v>
@@ -1525,7 +1568,7 @@
         <v>5</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S2" s="2" t="b">
         <v>1</v>
@@ -1533,38 +1576,36 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>138</v>
+        <v>26</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>133</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H3" s="2">
-        <v>6070</v>
+        <v>6639</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="9">
-        <v>16</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="1"/>
       <c r="L3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1586,34 +1627,34 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>74</v>
+        <v>34</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H4" s="2">
-        <v>5530</v>
+        <v>7048</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="2" t="s">
@@ -1637,34 +1678,34 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>78</v>
+        <v>23</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>58</v>
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H5" s="2">
-        <v>9084</v>
+        <v>8120</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="2" t="s">
@@ -1690,23 +1731,23 @@
       <c r="A6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>79</v>
+      <c r="B6" s="17" t="s">
+        <v>76</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H6" s="2">
         <v>4981</v>
@@ -1718,7 +1759,7 @@
         <v>35</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>2</v>
@@ -1739,30 +1780,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>80</v>
+        <v>25</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>134</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H7" s="2">
-        <v>5586</v>
+        <v>4798</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>6</v>
@@ -1770,7 +1811,9 @@
       <c r="J7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="L7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1792,28 +1835,28 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>81</v>
+        <v>38</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>61</v>
+        <v>38</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H8" s="2">
-        <v>6918</v>
+        <v>6996</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>6</v>
@@ -1821,7 +1864,9 @@
       <c r="J8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="L8" s="2" t="s">
         <v>2</v>
       </c>
@@ -1841,40 +1886,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>71</v>
+        <v>36</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>77</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H9" s="2">
-        <v>4996</v>
+        <v>5586</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="10">
-        <v>16</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="2" t="s">
         <v>2</v>
       </c>
@@ -1896,34 +1939,34 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>72</v>
+        <v>42</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H10" s="2">
-        <v>3556</v>
+        <v>4285</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="2" t="s">
@@ -1947,34 +1990,34 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>73</v>
+        <v>43</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H11" s="2">
-        <v>5343</v>
+        <v>4880</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="2" t="s">
@@ -1998,34 +2041,34 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>75</v>
+        <v>44</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>111</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H12" s="2">
-        <v>3329</v>
+        <v>2880</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="2" t="s">
@@ -2038,7 +2081,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2049,36 +2092,38 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>76</v>
+        <v>112</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H13" s="2">
-        <v>5685</v>
+        <v>6070</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="9">
+        <v>16</v>
+      </c>
       <c r="L13" s="2" t="s">
         <v>2</v>
       </c>
@@ -2092,7 +2137,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" s="2" t="b">
         <v>1</v>
@@ -2100,36 +2145,38 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>118</v>
+        <v>11</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H14" s="2">
-        <v>4798</v>
+        <v>4996</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="K14" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="K14" s="10">
+        <v>16</v>
+      </c>
       <c r="L14" s="2" t="s">
         <v>2</v>
       </c>
@@ -2151,34 +2198,34 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>129</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H15" s="2">
-        <v>6639</v>
+        <v>5530</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="2" t="s">
@@ -2202,34 +2249,34 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>130</v>
+        <v>12</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H16" s="2">
-        <v>5217</v>
+        <v>3556</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="2" t="s">
@@ -2253,34 +2300,34 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>131</v>
+        <v>15</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H17" s="2">
-        <v>7048</v>
+        <v>3329</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="2" t="s">
@@ -2304,34 +2351,34 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>113</v>
+        <v>16</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H18" s="2">
-        <v>3944</v>
+        <v>5685</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="2" t="s">
@@ -2347,7 +2394,7 @@
         <v>5</v>
       </c>
       <c r="R18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" s="2" t="b">
         <v>1</v>
@@ -2355,34 +2402,34 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>114</v>
+        <v>17</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H19" s="2">
-        <v>7133</v>
+        <v>5023</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="2" t="s">
@@ -2406,34 +2453,34 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>122</v>
+        <v>18</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>117</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H20" s="2">
-        <v>4285</v>
+        <v>6189</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="2" t="s">
@@ -2457,34 +2504,34 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>123</v>
+        <v>13</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>127</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H21" s="2">
-        <v>4880</v>
+        <v>5343</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="2" t="s">
@@ -2508,36 +2555,32 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="G22" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22" s="2">
-        <v>2880</v>
+        <v>97</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K22" s="1"/>
+        <v>128</v>
+      </c>
       <c r="L22" s="2" t="s">
         <v>2</v>
       </c>
@@ -2548,7 +2591,7 @@
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -2558,35 +2601,35 @@
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
-        <v>17</v>
+      <c r="A23" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="H23" s="2">
-        <v>5023</v>
+        <v>5217</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="2" t="s">
@@ -2609,35 +2652,35 @@
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
-        <v>18</v>
+      <c r="A24" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>98</v>
+        <v>19</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="H24" s="2">
-        <v>6189</v>
+        <v>4936</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="2" t="s">
@@ -2660,39 +2703,37 @@
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
-        <v>56</v>
+      <c r="A25" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>56</v>
+        <v>22</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="H25" s="2">
-        <v>6896</v>
+        <v>1786</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J25" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K25" s="1"/>
       <c r="L25" s="2" t="s">
         <v>2</v>
       </c>
@@ -2706,42 +2747,42 @@
         <v>5</v>
       </c>
       <c r="R25">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S25" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>23</v>
+      <c r="A26" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H26" s="2">
-        <v>8120</v>
+        <v>4060</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J26" s="13" t="s">
-        <v>21</v>
+      <c r="J26" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="2" t="s">
@@ -2764,35 +2805,35 @@
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
-        <v>19</v>
+      <c r="A27" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>57</v>
+        <v>27</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H27" s="2">
-        <v>4936</v>
+        <v>933</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="2" t="s">
@@ -2815,35 +2856,35 @@
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
-        <v>22</v>
+      <c r="A28" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>59</v>
+        <v>28</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H28" s="2">
-        <v>1786</v>
+        <v>4936</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="2" t="s">
@@ -2866,35 +2907,35 @@
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
-        <v>24</v>
+      <c r="A29" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H29" s="2">
-        <v>4060</v>
+        <v>5356</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="2" t="s">
@@ -2917,35 +2958,35 @@
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
-        <v>27</v>
+      <c r="A30" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>83</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H30" s="2">
-        <v>933</v>
+        <v>6758</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="2" t="s">
@@ -2968,35 +3009,35 @@
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
-        <v>28</v>
+      <c r="A31" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H31" s="2">
-        <v>4936</v>
+        <v>4871</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="2" t="s">
@@ -3009,7 +3050,7 @@
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -3019,35 +3060,35 @@
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
-        <v>29</v>
+      <c r="A32" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>132</v>
+        <v>30</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H32" s="2">
-        <v>5356</v>
+        <v>6387</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="2" t="s">
@@ -3070,35 +3111,35 @@
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
-        <v>30</v>
+      <c r="A33" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H33" s="2">
-        <v>6387</v>
+        <v>6758</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="2" t="s">
@@ -3121,35 +3162,35 @@
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
-        <v>31</v>
+      <c r="A34" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H34" s="2">
-        <v>6758</v>
+        <v>6918</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="2" t="s">
@@ -3172,35 +3213,35 @@
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
-        <v>33</v>
+      <c r="A35" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H35" s="2">
-        <v>4871</v>
+        <v>3944</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="2" t="s">
@@ -3213,7 +3254,7 @@
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -3222,16 +3263,164 @@
         <v>1</v>
       </c>
     </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A36" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H36" s="2">
+        <v>7133</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K36" s="1"/>
+      <c r="L36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R36">
+        <v>1</v>
+      </c>
+      <c r="S36" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A37" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H37" s="2">
+        <v>9084</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K37" s="1"/>
+      <c r="L37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A38" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K38" s="1"/>
+      <c r="L38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q38">
+        <v>1</v>
+      </c>
+      <c r="R38" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S35">
-    <sortCondition ref="G2:G35"/>
-    <sortCondition ref="F2:F35"/>
-    <sortCondition ref="I2:I35"/>
-    <sortCondition ref="J2:J35"/>
-    <sortCondition ref="K2:K35"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S38">
+    <sortCondition ref="G2:G38"/>
+    <sortCondition ref="I2:I38"/>
+    <sortCondition ref="J2:J38"/>
+    <sortCondition ref="K2:K38"/>
   </sortState>
-  <conditionalFormatting sqref="R36:R1048576">
-    <cfRule type="colorScale" priority="97">
+  <conditionalFormatting sqref="R39:R1048576">
+    <cfRule type="colorScale" priority="106">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3243,7 +3432,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="colorScale" priority="39">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3255,7 +3444,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S1">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3266,13 +3455,25 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G35">
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="excluded">
+  <conditionalFormatting sqref="G23:G36 G2:G21">
+    <cfRule type="containsText" dxfId="3" priority="24" operator="containsText" text="excluded">
       <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R35">
-    <cfRule type="colorScale" priority="103">
+  <conditionalFormatting sqref="Q25">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R31">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3283,6 +3484,45 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R26:R30 R2:R24 R38 R32:R36">
+    <cfRule type="colorScale" priority="127">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R37">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G37)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G38">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G38)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/tabular/reference/ervr/ervr_data.xlsx
+++ b/tabular/reference/ervr/ervr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF530490-6141-A046-B9CA-357EA67E0604}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE10E827-498B-2D49-989C-D61C90811426}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="860" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1240" yWindow="520" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="137">
   <si>
     <t>sequenceID</t>
   </si>
@@ -251,9 +251,6 @@
     <t>ERV-3.Lambda.52</t>
   </si>
   <si>
-    <t>ERV-3.Lambda.57</t>
-  </si>
-  <si>
     <t>ERV-3.Lambda.40</t>
   </si>
   <si>
@@ -263,21 +260,9 @@
     <t>ERV-3.Lambda.74</t>
   </si>
   <si>
-    <t>ERV-1.Rho.Rb.31</t>
-  </si>
-  <si>
-    <t>ERV-1.Rho.Rb.39</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta.HF.52A</t>
   </si>
   <si>
-    <t>ERV-1.Zeta.19</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.35</t>
-  </si>
-  <si>
     <t>medium reiteration frequency repeat 101</t>
   </si>
   <si>
@@ -359,9 +344,6 @@
     <t>lineage_id</t>
   </si>
   <si>
-    <t>Unclassified</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta.W9P.P</t>
   </si>
   <si>
@@ -371,33 +353,9 @@
     <t>HF</t>
   </si>
   <si>
-    <t>ERVR-1.Zeta.MER41</t>
-  </si>
-  <si>
-    <t>ERVR-1.Zeta.MER57</t>
-  </si>
-  <si>
-    <t>Rhoretrovirus</t>
-  </si>
-  <si>
     <t>ERVR-1.Theta.LOR1</t>
   </si>
   <si>
-    <t>ERVR-1.Theta.37</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.43</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.38</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.MER31</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.MER21</t>
-  </si>
-  <si>
     <t>ERVR-1.Zeta.MER83A</t>
   </si>
   <si>
@@ -419,36 +377,12 @@
     <t>excluded</t>
   </si>
   <si>
-    <t>ERVR-1.Theta.101</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.MER61</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.MER89</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.MER34b</t>
-  </si>
-  <si>
-    <t>ERVR-1.Unclassified.MER4</t>
-  </si>
-  <si>
-    <t>ERVR-1.Unclassified.MER4b</t>
-  </si>
-  <si>
-    <t>ERVR-1.Unclassified.MER65</t>
-  </si>
-  <si>
     <t>ERVR-3.Lambda.70</t>
   </si>
   <si>
     <t>ERVR-3.Lambda.76</t>
   </si>
   <si>
-    <t>ERVR-3.Lambda.16A3</t>
-  </si>
-  <si>
     <t>ERV-1.Eta.E.HQ</t>
   </si>
   <si>
@@ -465,6 +399,48 @@
   </si>
   <si>
     <t>NK</t>
+  </si>
+  <si>
+    <t>sublineage</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus L68</t>
+  </si>
+  <si>
+    <t>HERV-L68</t>
+  </si>
+  <si>
+    <t>ERV-3.Sigma.57</t>
+  </si>
+  <si>
+    <t>Sigmaretrovirus</t>
+  </si>
+  <si>
+    <t>endogenous retrovirus L47</t>
+  </si>
+  <si>
+    <t>ERV-L47</t>
+  </si>
+  <si>
+    <t>ERV-3.Sigma</t>
+  </si>
+  <si>
+    <t>ERV-3.Sigma.47</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.24.101</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.43</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.24.MER89</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda.16A3</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.HF.19</t>
   </si>
 </sst>
 </file>
@@ -630,7 +606,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -843,6 +819,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8AD8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5FC79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39994506668294322"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF85FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1007,7 +1013,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1032,6 +1038,11 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1077,7 +1088,37 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1092,7 +1133,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF85FF"/>
       <color rgb="FFFF8AD8"/>
+      <color rgb="FFD5FC79"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1403,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1424,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>45</v>
@@ -1433,13 +1476,13 @@
         <v>46</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>1</v>
@@ -1475,42 +1518,42 @@
         <v>69</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>140</v>
+        <v>56</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H2" s="2">
-        <v>6996</v>
+        <v>6896</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>35</v>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>2</v>
@@ -1533,38 +1576,36 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>138</v>
+        <v>26</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>132</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2">
-        <v>6070</v>
+        <v>6639</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="9">
-        <v>16</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="1"/>
       <c r="L3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1586,34 +1627,34 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>74</v>
+        <v>34</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>134</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H4" s="2">
-        <v>5530</v>
+        <v>7048</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="2" t="s">
@@ -1637,34 +1678,34 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>78</v>
+        <v>23</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>107</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>58</v>
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2">
-        <v>9084</v>
+        <v>8120</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="2" t="s">
@@ -1690,23 +1731,23 @@
       <c r="A6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>79</v>
+      <c r="B6" s="17" t="s">
+        <v>76</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2">
         <v>4981</v>
@@ -1718,7 +1759,7 @@
         <v>35</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>2</v>
@@ -1739,30 +1780,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>80</v>
+        <v>25</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>133</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2">
-        <v>5586</v>
+        <v>4798</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>6</v>
@@ -1770,7 +1811,9 @@
       <c r="J7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="L7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1792,28 +1835,28 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>81</v>
+        <v>38</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>61</v>
+        <v>38</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>104</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2">
-        <v>6918</v>
+        <v>6996</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>6</v>
@@ -1821,7 +1864,9 @@
       <c r="J8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="L8" s="2" t="s">
         <v>2</v>
       </c>
@@ -1841,40 +1886,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>71</v>
+        <v>36</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>136</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H9" s="2">
-        <v>4996</v>
+        <v>5586</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="10">
-        <v>16</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="2" t="s">
         <v>2</v>
       </c>
@@ -1896,34 +1939,34 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>72</v>
+        <v>42</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H10" s="2">
-        <v>3556</v>
+        <v>4285</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="2" t="s">
@@ -1947,34 +1990,34 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>73</v>
+        <v>43</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H11" s="2">
-        <v>5343</v>
+        <v>4880</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="2" t="s">
@@ -1998,34 +2041,34 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>75</v>
+        <v>44</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H12" s="2">
-        <v>3329</v>
+        <v>2880</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="2" t="s">
@@ -2038,7 +2081,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2049,36 +2092,38 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>76</v>
+        <v>111</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H13" s="2">
-        <v>5685</v>
+        <v>6070</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="9">
+        <v>16</v>
+      </c>
       <c r="L13" s="2" t="s">
         <v>2</v>
       </c>
@@ -2092,7 +2137,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" s="2" t="b">
         <v>1</v>
@@ -2100,36 +2145,38 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>118</v>
+        <v>11</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H14" s="2">
-        <v>4798</v>
+        <v>4996</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="K14" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="K14" s="10">
+        <v>16</v>
+      </c>
       <c r="L14" s="2" t="s">
         <v>2</v>
       </c>
@@ -2151,34 +2198,34 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>129</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H15" s="2">
-        <v>6639</v>
+        <v>5530</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="2" t="s">
@@ -2202,34 +2249,34 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>130</v>
+        <v>12</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H16" s="2">
-        <v>5217</v>
+        <v>3556</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="2" t="s">
@@ -2253,34 +2300,34 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>131</v>
+        <v>15</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H17" s="2">
-        <v>7048</v>
+        <v>3329</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="2" t="s">
@@ -2304,34 +2351,34 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>113</v>
+        <v>16</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H18" s="2">
-        <v>3944</v>
+        <v>5685</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="2" t="s">
@@ -2347,7 +2394,7 @@
         <v>5</v>
       </c>
       <c r="R18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" s="2" t="b">
         <v>1</v>
@@ -2355,34 +2402,34 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>114</v>
+        <v>17</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H19" s="2">
-        <v>7133</v>
+        <v>5023</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="2" t="s">
@@ -2406,34 +2453,34 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>122</v>
+        <v>18</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H20" s="2">
-        <v>4285</v>
+        <v>6189</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="2" t="s">
@@ -2457,34 +2504,34 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>123</v>
+        <v>13</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>126</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H21" s="2">
-        <v>4880</v>
+        <v>5343</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="2" t="s">
@@ -2508,36 +2555,32 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>124</v>
+        <v>129</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>131</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22" s="2">
-        <v>2880</v>
-      </c>
       <c r="I22" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K22" s="1"/>
+        <v>127</v>
+      </c>
       <c r="L22" s="2" t="s">
         <v>2</v>
       </c>
@@ -2548,7 +2591,7 @@
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -2558,35 +2601,35 @@
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
-        <v>17</v>
+      <c r="A23" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="H23" s="2">
-        <v>5023</v>
+        <v>5217</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="2" t="s">
@@ -2609,35 +2652,35 @@
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
-        <v>18</v>
+      <c r="A24" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>101</v>
+      <c r="G24" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="H24" s="2">
-        <v>6189</v>
+        <v>4936</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="2" t="s">
@@ -2660,39 +2703,37 @@
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
-        <v>56</v>
+      <c r="A25" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>56</v>
+        <v>22</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="H25" s="2">
-        <v>6896</v>
+        <v>1786</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J25" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K25" s="1"/>
       <c r="L25" s="2" t="s">
         <v>2</v>
       </c>
@@ -2706,42 +2747,42 @@
         <v>5</v>
       </c>
       <c r="R25">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S25" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>23</v>
+      <c r="A26" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H26" s="2">
-        <v>8120</v>
+        <v>4060</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J26" s="13" t="s">
-        <v>21</v>
+      <c r="J26" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="2" t="s">
@@ -2764,35 +2805,35 @@
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
-        <v>19</v>
+      <c r="A27" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>57</v>
+        <v>27</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H27" s="2">
-        <v>4936</v>
+        <v>933</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="2" t="s">
@@ -2815,35 +2856,35 @@
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
-        <v>22</v>
+      <c r="A28" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>59</v>
+        <v>28</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H28" s="2">
-        <v>1786</v>
+        <v>4936</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="2" t="s">
@@ -2866,35 +2907,35 @@
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
-        <v>24</v>
+      <c r="A29" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H29" s="2">
-        <v>4060</v>
+        <v>5356</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="2" t="s">
@@ -2917,35 +2958,35 @@
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
-        <v>27</v>
+      <c r="A30" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H30" s="2">
-        <v>933</v>
+        <v>6758</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="2" t="s">
@@ -2968,35 +3009,35 @@
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
-        <v>28</v>
+      <c r="A31" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>84</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H31" s="2">
-        <v>4936</v>
+        <v>4871</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="2" t="s">
@@ -3009,7 +3050,7 @@
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -3019,35 +3060,35 @@
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
-        <v>29</v>
+      <c r="A32" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>132</v>
+        <v>30</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H32" s="2">
-        <v>5356</v>
+        <v>6387</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="2" t="s">
@@ -3070,35 +3111,35 @@
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
-        <v>30</v>
+      <c r="A33" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H33" s="2">
-        <v>6387</v>
+        <v>6758</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="2" t="s">
@@ -3121,35 +3162,35 @@
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
-        <v>31</v>
+      <c r="A34" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H34" s="2">
-        <v>6758</v>
+        <v>6918</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="2" t="s">
@@ -3172,35 +3213,35 @@
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
-        <v>33</v>
+      <c r="A35" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H35" s="2">
-        <v>4871</v>
+        <v>3944</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="2" t="s">
@@ -3213,7 +3254,7 @@
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -3222,16 +3263,164 @@
         <v>1</v>
       </c>
     </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A36" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H36" s="2">
+        <v>7133</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K36" s="1"/>
+      <c r="L36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R36">
+        <v>1</v>
+      </c>
+      <c r="S36" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A37" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H37" s="2">
+        <v>9084</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K37" s="1"/>
+      <c r="L37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A38" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K38" s="1"/>
+      <c r="L38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="Q38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R38">
+        <v>1</v>
+      </c>
+      <c r="S38" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S35">
-    <sortCondition ref="G2:G35"/>
-    <sortCondition ref="F2:F35"/>
-    <sortCondition ref="I2:I35"/>
-    <sortCondition ref="J2:J35"/>
-    <sortCondition ref="K2:K35"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S38">
+    <sortCondition ref="G2:G38"/>
+    <sortCondition ref="I2:I38"/>
+    <sortCondition ref="J2:J38"/>
+    <sortCondition ref="K2:K38"/>
   </sortState>
-  <conditionalFormatting sqref="R36:R1048576">
-    <cfRule type="colorScale" priority="97">
+  <conditionalFormatting sqref="R39:R1048576">
+    <cfRule type="colorScale" priority="107">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3243,7 +3432,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="colorScale" priority="39">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3255,7 +3444,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S1">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3266,13 +3455,64 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G35">
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="excluded">
+  <conditionalFormatting sqref="G23:G36 G2:G21">
+    <cfRule type="containsText" dxfId="3" priority="25" operator="containsText" text="excluded">
       <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R35">
-    <cfRule type="colorScale" priority="103">
+  <conditionalFormatting sqref="Q25">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R26:R30 S38 R32:R36 R2:R24">
+    <cfRule type="colorScale" priority="128">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R37">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G37)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G38">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G38)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R31">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/tabular/reference/ervr/ervr_data.xlsx
+++ b/tabular/reference/ervr/ervr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB76F8CD-FF49-A049-8F8A-ED386B79CE36}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2EF283-6AB4-E54E-8A84-8CCA826B6C85}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="1380" windowWidth="25540" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="2800" windowWidth="25980" windowHeight="14960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="110">
   <si>
     <t>sequenceID</t>
   </si>
@@ -74,51 +74,18 @@
     <t>MER-76</t>
   </si>
   <si>
-    <t>HERV-31</t>
-  </si>
-  <si>
-    <t>HERV-39</t>
-  </si>
-  <si>
     <t>Thetaretrovirus</t>
   </si>
   <si>
-    <t>HERV-38</t>
-  </si>
-  <si>
     <t>LOR-1</t>
   </si>
   <si>
-    <t>LTR-37</t>
-  </si>
-  <si>
     <t>LTR-43</t>
   </si>
   <si>
     <t>MER-101</t>
   </si>
   <si>
-    <t>MER-21</t>
-  </si>
-  <si>
-    <t>MER-31</t>
-  </si>
-  <si>
-    <t>MER-34B</t>
-  </si>
-  <si>
-    <t>MER-4</t>
-  </si>
-  <si>
-    <t>MER-4B</t>
-  </si>
-  <si>
-    <t>MER-61</t>
-  </si>
-  <si>
-    <t>MER-65</t>
-  </si>
-  <si>
     <t>MER-89</t>
   </si>
   <si>
@@ -128,21 +95,12 @@
     <t>HERV-19</t>
   </si>
   <si>
-    <t>HERV-35</t>
-  </si>
-  <si>
     <t>HERV-G25</t>
   </si>
   <si>
-    <t>MER-41</t>
-  </si>
-  <si>
     <t>MER-52A</t>
   </si>
   <si>
-    <t>MER-57</t>
-  </si>
-  <si>
     <t>MER-83A</t>
   </si>
   <si>
@@ -170,21 +128,9 @@
     <t>pubmed_id</t>
   </si>
   <si>
-    <t>human endogenous retrovirus 31</t>
-  </si>
-  <si>
-    <t>human endogenous retrovirus 39</t>
-  </si>
-  <si>
-    <t>human endogenous retrovirus 38</t>
-  </si>
-  <si>
     <t>human endogenous retrovirus 19</t>
   </si>
   <si>
-    <t>human endogenous retrovirus 35</t>
-  </si>
-  <si>
     <t>human endogenous retrovirus G25</t>
   </si>
   <si>
@@ -209,60 +155,15 @@
     <t>ERV-3.Lambda.L</t>
   </si>
   <si>
-    <t>ERV-3.Lambda.16</t>
-  </si>
-  <si>
-    <t>ERV-3.Lambda.52</t>
-  </si>
-  <si>
-    <t>ERV-3.Lambda.40</t>
-  </si>
-  <si>
-    <t>ERV-3.Lambda.53</t>
-  </si>
-  <si>
-    <t>ERV-3.Lambda.74</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.HF.52A</t>
-  </si>
-  <si>
     <t>medium reiteration frequency repeat 101</t>
   </si>
   <si>
-    <t>medium reiteration frequency repeat 21</t>
-  </si>
-  <si>
-    <t>medium reiteration frequency repeat 31</t>
-  </si>
-  <si>
-    <t>medium reiteration frequency repeat 34B</t>
-  </si>
-  <si>
-    <t>medium reiteration frequency repeat 4</t>
-  </si>
-  <si>
-    <t>medium reiteration frequency repeat 4B</t>
-  </si>
-  <si>
-    <t>medium reiteration frequency repeat 61</t>
-  </si>
-  <si>
-    <t>medium reiteration frequency repeat 65</t>
-  </si>
-  <si>
     <t>medium reiteration frequency repeat 89</t>
   </si>
   <si>
     <t>medium reiteration frequency repeat 52A</t>
   </si>
   <si>
-    <t>medium reiteration frequency repeat 41</t>
-  </si>
-  <si>
-    <t>medium reiteration frequency repeat 57</t>
-  </si>
-  <si>
     <t>medium reiteration frequency repeat 83A</t>
   </si>
   <si>
@@ -287,9 +188,6 @@
     <t>accepted</t>
   </si>
   <si>
-    <t>repeat_group</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta</t>
   </si>
   <si>
@@ -311,18 +209,6 @@
     <t>HF</t>
   </si>
   <si>
-    <t>ERVR-1.Theta.LOR1</t>
-  </si>
-  <si>
-    <t>ERVR-1.Zeta.MER83A</t>
-  </si>
-  <si>
-    <t>ERVR-1.Zeta.MER83B</t>
-  </si>
-  <si>
-    <t>ERVR-1.Zeta.MER84</t>
-  </si>
-  <si>
     <t>ERV3-16A3</t>
   </si>
   <si>
@@ -332,9 +218,6 @@
     <t>parent_lineage</t>
   </si>
   <si>
-    <t>excluded</t>
-  </si>
-  <si>
     <t>ERVR-3.Lambda.70</t>
   </si>
   <si>
@@ -347,18 +230,6 @@
     <t>erv_derived_repeat</t>
   </si>
   <si>
-    <t>degraded_erv_group</t>
-  </si>
-  <si>
-    <t>NK</t>
-  </si>
-  <si>
-    <t>human endogenous retrovirus L68</t>
-  </si>
-  <si>
-    <t>HERV-L68</t>
-  </si>
-  <si>
     <t>ERV-3.Sigma.57</t>
   </si>
   <si>
@@ -374,24 +245,12 @@
     <t>ERV-3.Sigma</t>
   </si>
   <si>
-    <t>ERV-3.Sigma.47</t>
-  </si>
-  <si>
     <t>ERVR-1.Theta.24.101</t>
   </si>
   <si>
     <t>ERVR-1.Zeta.43</t>
   </si>
   <si>
-    <t>ERVR-1.Theta.24.MER89</t>
-  </si>
-  <si>
-    <t>ERV-3.Lambda.16A3</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.HF.19</t>
-  </si>
-  <si>
     <t>legacy_name</t>
   </si>
   <si>
@@ -452,13 +311,55 @@
     <t>Sigma-Lambda</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>classification_basis</t>
   </si>
   <si>
     <t>repeat_family</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.HF.52A</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.HF.19</t>
+  </si>
+  <si>
+    <t>ERVR-3.Lambda.16A3</t>
+  </si>
+  <si>
+    <t>ERVR-3.Lambda.16</t>
+  </si>
+  <si>
+    <t>ERVR-3.Lambda.40</t>
+  </si>
+  <si>
+    <t>ERVR-3.Lambda.52</t>
+  </si>
+  <si>
+    <t>ERVR-3.Lambda.53</t>
+  </si>
+  <si>
+    <t>ERVR-3.Lambda.74</t>
+  </si>
+  <si>
+    <t>ERVR-3.Sigma.57</t>
+  </si>
+  <si>
+    <t>ERVR-3.Sigma.47</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.24.89</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.24.LOR1</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.83B</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.83A</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.84</t>
   </si>
 </sst>
 </file>
@@ -624,7 +525,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -837,12 +738,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8AD8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1025,7 +920,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1045,12 +940,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1105,27 +998,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1463,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1491,121 +1364,121 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="V1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="W1" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="J1" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="N1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="P1" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q1" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="T1" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="U1" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="W1" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="X1" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="Y1" s="17" t="s">
-        <v>132</v>
+      <c r="X1" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y1" s="15" t="s">
+        <v>85</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>115</v>
+        <v>17</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="2" t="b">
@@ -1614,31 +1487,31 @@
       <c r="N2" s="2">
         <v>6639</v>
       </c>
-      <c r="O2" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P2" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q2" s="19" t="s">
-        <v>137</v>
+      <c r="O2" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S2" s="2"/>
       <c r="T2" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
-      <c r="W2" s="19">
-        <v>0</v>
-      </c>
-      <c r="X2" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="19">
+      <c r="W2" s="17">
+        <v>0</v>
+      </c>
+      <c r="X2" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="17">
         <v>0</v>
       </c>
       <c r="Z2" s="2"/>
@@ -1648,35 +1521,35 @@
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>117</v>
+        <v>18</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="2" t="b">
@@ -1685,31 +1558,31 @@
       <c r="N3" s="2">
         <v>7048</v>
       </c>
-      <c r="O3" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>137</v>
+      <c r="O3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S3" s="2"/>
       <c r="T3" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
-      <c r="W3" s="19">
-        <v>0</v>
-      </c>
-      <c r="X3" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="19">
+      <c r="W3" s="17">
+        <v>0</v>
+      </c>
+      <c r="X3" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="17">
         <v>0</v>
       </c>
       <c r="Z3" s="2"/>
@@ -1719,35 +1592,35 @@
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>93</v>
+        <v>15</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="2" t="b">
@@ -1756,31 +1629,31 @@
       <c r="N4" s="2">
         <v>8120</v>
       </c>
-      <c r="O4" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P4" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q4" s="19" t="s">
-        <v>137</v>
+      <c r="O4" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S4" s="2"/>
       <c r="T4" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
-      <c r="W4" s="19">
-        <v>0</v>
-      </c>
-      <c r="X4" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="19">
+      <c r="W4" s="17">
+        <v>0</v>
+      </c>
+      <c r="X4" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="17">
         <v>0</v>
       </c>
       <c r="Z4" s="2"/>
@@ -1790,38 +1663,38 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>64</v>
+        <v>22</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="M5" s="2" t="b">
         <v>1</v>
@@ -1829,31 +1702,31 @@
       <c r="N5" s="2">
         <v>4981</v>
       </c>
-      <c r="O5" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P5" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q5" s="19" t="s">
-        <v>137</v>
+      <c r="O5" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S5" s="2"/>
       <c r="T5" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
-      <c r="W5" s="19">
-        <v>0</v>
-      </c>
-      <c r="X5" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="19">
+      <c r="W5" s="17">
+        <v>0</v>
+      </c>
+      <c r="X5" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="17">
         <v>0</v>
       </c>
       <c r="Z5" s="2"/>
@@ -1863,38 +1736,38 @@
     </row>
     <row r="6" spans="1:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>116</v>
+        <v>16</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="M6" s="2" t="b">
         <v>1</v>
@@ -1902,31 +1775,31 @@
       <c r="N6" s="2">
         <v>4798</v>
       </c>
-      <c r="O6" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P6" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q6" s="19" t="s">
-        <v>137</v>
+      <c r="O6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S6" s="2"/>
       <c r="T6" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
-      <c r="W6" s="19">
-        <v>0</v>
-      </c>
-      <c r="X6" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="19">
+      <c r="W6" s="17">
+        <v>0</v>
+      </c>
+      <c r="X6" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="17">
         <v>0</v>
       </c>
       <c r="Z6" s="2"/>
@@ -1936,38 +1809,38 @@
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>1</v>
@@ -1975,31 +1848,31 @@
       <c r="N7" s="2">
         <v>6996</v>
       </c>
-      <c r="O7" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P7" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q7" s="19" t="s">
-        <v>137</v>
+      <c r="O7" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q7" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="2"/>
       <c r="T7" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
-      <c r="W7" s="19">
-        <v>0</v>
-      </c>
-      <c r="X7" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="19">
+      <c r="W7" s="17">
+        <v>0</v>
+      </c>
+      <c r="X7" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="17">
         <v>0</v>
       </c>
       <c r="Z7" s="2"/>
@@ -2009,35 +1882,35 @@
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>119</v>
+        <v>20</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>96</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="2" t="b">
@@ -2046,31 +1919,31 @@
       <c r="N8" s="2">
         <v>5586</v>
       </c>
-      <c r="O8" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P8" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q8" s="19" t="s">
-        <v>137</v>
+      <c r="O8" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S8" s="2"/>
       <c r="T8" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
-      <c r="W8" s="19">
-        <v>0</v>
-      </c>
-      <c r="X8" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="19">
+      <c r="W8" s="17">
+        <v>0</v>
+      </c>
+      <c r="X8" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="17">
         <v>0</v>
       </c>
       <c r="Z8" s="2"/>
@@ -2080,35 +1953,35 @@
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="2" t="b">
@@ -2117,31 +1990,31 @@
       <c r="N9" s="2">
         <v>4285</v>
       </c>
-      <c r="O9" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P9" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q9" s="19" t="s">
-        <v>137</v>
+      <c r="O9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S9" s="2"/>
       <c r="T9" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
-      <c r="W9" s="19">
-        <v>0</v>
-      </c>
-      <c r="X9" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="19">
+      <c r="W9" s="17">
+        <v>0</v>
+      </c>
+      <c r="X9" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="17">
         <v>0</v>
       </c>
       <c r="Z9" s="2"/>
@@ -2151,35 +2024,35 @@
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>95</v>
+        <v>24</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="2" t="b">
@@ -2188,31 +2061,31 @@
       <c r="N10" s="2">
         <v>4880</v>
       </c>
-      <c r="O10" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P10" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q10" s="19" t="s">
-        <v>137</v>
+      <c r="O10" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P10" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S10" s="2"/>
       <c r="T10" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
-      <c r="W10" s="19">
-        <v>0</v>
-      </c>
-      <c r="X10" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="19">
+      <c r="W10" s="17">
+        <v>0</v>
+      </c>
+      <c r="X10" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="17">
         <v>0</v>
       </c>
       <c r="Z10" s="2"/>
@@ -2222,35 +2095,35 @@
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>96</v>
+        <v>25</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="2" t="b">
@@ -2259,31 +2132,31 @@
       <c r="N11" s="2">
         <v>2880</v>
       </c>
-      <c r="O11" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P11" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>137</v>
+      <c r="O11" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P11" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S11" s="2"/>
       <c r="T11" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
-      <c r="W11" s="19">
-        <v>0</v>
-      </c>
-      <c r="X11" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="19">
+      <c r="W11" s="17">
+        <v>0</v>
+      </c>
+      <c r="X11" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="17">
         <v>0</v>
       </c>
       <c r="Z11" s="2"/>
@@ -2293,72 +2166,70 @@
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="8">
-        <v>16</v>
-      </c>
+      <c r="L12" s="8"/>
       <c r="M12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N12" s="2">
         <v>6070</v>
       </c>
-      <c r="O12" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P12" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>137</v>
+      <c r="O12" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P12" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S12" s="2"/>
       <c r="T12" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
-      <c r="W12" s="19">
-        <v>0</v>
-      </c>
-      <c r="X12" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="19">
+      <c r="W12" s="17">
+        <v>0</v>
+      </c>
+      <c r="X12" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="17">
         <v>0</v>
       </c>
       <c r="Z12" s="2"/>
@@ -2370,70 +2241,68 @@
       <c r="A13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>59</v>
+      <c r="B13" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L13" s="9">
-        <v>16</v>
-      </c>
+      <c r="L13" s="9"/>
       <c r="M13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N13" s="2">
         <v>4996</v>
       </c>
-      <c r="O13" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P13" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q13" s="19" t="s">
-        <v>137</v>
+      <c r="O13" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P13" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q13" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S13" s="2"/>
       <c r="T13" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
-      <c r="W13" s="19">
-        <v>0</v>
-      </c>
-      <c r="X13" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="19">
+      <c r="W13" s="17">
+        <v>0</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="17">
         <v>0</v>
       </c>
       <c r="Z13" s="2"/>
@@ -2445,32 +2314,32 @@
       <c r="A14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>61</v>
+      <c r="B14" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>5</v>
@@ -2482,31 +2351,31 @@
       <c r="N14" s="2">
         <v>5530</v>
       </c>
-      <c r="O14" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P14" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q14" s="19" t="s">
-        <v>137</v>
+      <c r="O14" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P14" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S14" s="2"/>
       <c r="T14" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
-      <c r="W14" s="19">
-        <v>0</v>
-      </c>
-      <c r="X14" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="19">
+      <c r="W14" s="17">
+        <v>0</v>
+      </c>
+      <c r="X14" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="17">
         <v>0</v>
       </c>
       <c r="Z14" s="2"/>
@@ -2518,32 +2387,32 @@
       <c r="A15" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>60</v>
+      <c r="B15" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>5</v>
@@ -2555,31 +2424,31 @@
       <c r="N15" s="2">
         <v>3556</v>
       </c>
-      <c r="O15" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P15" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q15" s="19" t="s">
-        <v>137</v>
+      <c r="O15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P15" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S15" s="2"/>
       <c r="T15" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
-      <c r="W15" s="19">
-        <v>0</v>
-      </c>
-      <c r="X15" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="19">
+      <c r="W15" s="17">
+        <v>0</v>
+      </c>
+      <c r="X15" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="17">
         <v>0</v>
       </c>
       <c r="Z15" s="2"/>
@@ -2591,32 +2460,32 @@
       <c r="A16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>62</v>
+      <c r="B16" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>5</v>
@@ -2628,31 +2497,31 @@
       <c r="N16" s="2">
         <v>3329</v>
       </c>
-      <c r="O16" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P16" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q16" s="19" t="s">
-        <v>137</v>
+      <c r="O16" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P16" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S16" s="2"/>
       <c r="T16" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
-      <c r="W16" s="19">
-        <v>0</v>
-      </c>
-      <c r="X16" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="19">
+      <c r="W16" s="17">
+        <v>0</v>
+      </c>
+      <c r="X16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="17">
         <v>0</v>
       </c>
       <c r="Z16" s="2"/>
@@ -2664,32 +2533,32 @@
       <c r="A17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>63</v>
+      <c r="B17" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>5</v>
@@ -2701,31 +2570,31 @@
       <c r="N17" s="2">
         <v>5685</v>
       </c>
-      <c r="O17" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P17" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q17" s="19" t="s">
-        <v>137</v>
+      <c r="O17" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P17" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q17" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S17" s="2"/>
       <c r="T17" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
-      <c r="W17" s="19">
-        <v>0</v>
-      </c>
-      <c r="X17" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="19">
+      <c r="W17" s="17">
+        <v>0</v>
+      </c>
+      <c r="X17" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="17">
         <v>0</v>
       </c>
       <c r="Z17" s="2"/>
@@ -2737,32 +2606,32 @@
       <c r="A18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>101</v>
+      <c r="B18" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>5</v>
@@ -2774,31 +2643,31 @@
       <c r="N18" s="2">
         <v>5023</v>
       </c>
-      <c r="O18" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P18" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q18" s="19" t="s">
-        <v>137</v>
+      <c r="O18" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P18" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q18" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S18" s="2"/>
       <c r="T18" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
-      <c r="W18" s="19">
-        <v>0</v>
-      </c>
-      <c r="X18" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="19">
+      <c r="W18" s="17">
+        <v>0</v>
+      </c>
+      <c r="X18" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="17">
         <v>0</v>
       </c>
       <c r="Z18" s="2"/>
@@ -2810,32 +2679,32 @@
       <c r="A19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>102</v>
+      <c r="B19" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>5</v>
@@ -2847,31 +2716,31 @@
       <c r="N19" s="2">
         <v>6189</v>
       </c>
-      <c r="O19" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P19" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q19" s="19" t="s">
-        <v>137</v>
+      <c r="O19" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P19" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q19" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
-      <c r="W19" s="19">
-        <v>0</v>
-      </c>
-      <c r="X19" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="19">
+      <c r="W19" s="17">
+        <v>0</v>
+      </c>
+      <c r="X19" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="17">
         <v>0</v>
       </c>
       <c r="Z19" s="2"/>
@@ -2883,35 +2752,35 @@
       <c r="A20" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>109</v>
+      <c r="B20" s="14" t="s">
+        <v>103</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="2" t="b">
@@ -2920,31 +2789,31 @@
       <c r="N20" s="2">
         <v>5343</v>
       </c>
-      <c r="O20" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P20" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q20" s="19" t="s">
-        <v>137</v>
+      <c r="O20" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P20" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q20" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S20" s="2"/>
       <c r="T20" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
-      <c r="W20" s="19">
-        <v>0</v>
-      </c>
-      <c r="X20" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="19">
+      <c r="W20" s="17">
+        <v>0</v>
+      </c>
+      <c r="X20" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="17">
         <v>0</v>
       </c>
       <c r="Z20" s="2"/>
@@ -2954,66 +2823,66 @@
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>114</v>
+        <v>69</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="M21" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="O21" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P21" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q21" s="19" t="s">
-        <v>137</v>
+      <c r="O21" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="P21" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q21" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S21" s="2"/>
       <c r="T21" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
-      <c r="W21" s="19">
-        <v>0</v>
-      </c>
-      <c r="X21" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="19">
+      <c r="W21" s="17">
+        <v>0</v>
+      </c>
+      <c r="X21" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="17">
         <v>0</v>
       </c>
       <c r="Z21" s="2"/>
@@ -3021,1175 +2890,20 @@
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A22" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L22" s="1"/>
-      <c r="M22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N22" s="2">
-        <v>5217</v>
-      </c>
-      <c r="O22" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P22" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q22" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="19">
-        <v>0</v>
-      </c>
-      <c r="X22" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
-      <c r="AB22" s="2"/>
-      <c r="AC22" s="2"/>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="5"/>
-      <c r="K23" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L23" s="1"/>
-      <c r="M23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N23" s="2">
-        <v>4936</v>
-      </c>
-      <c r="O23" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P23" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q23" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="19">
-        <v>0</v>
-      </c>
-      <c r="X23" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="2"/>
-      <c r="AA23" s="2"/>
-      <c r="AB23" s="2"/>
-      <c r="AC23" s="2"/>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="5"/>
-      <c r="K24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L24" s="1"/>
-      <c r="M24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N24" s="2">
-        <v>1786</v>
-      </c>
-      <c r="O24" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P24" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q24" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="19">
-        <v>0</v>
-      </c>
-      <c r="X24" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
-      <c r="AC24" s="2"/>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A25" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J25" s="5"/>
-      <c r="K25" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L25" s="1"/>
-      <c r="M25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N25" s="2">
-        <v>4060</v>
-      </c>
-      <c r="O25" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P25" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q25" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="19">
-        <v>0</v>
-      </c>
-      <c r="X25" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="2"/>
-      <c r="AA25" s="2"/>
-      <c r="AB25" s="2"/>
-      <c r="AC25" s="2"/>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A26" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L26" s="1"/>
-      <c r="M26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N26" s="2">
-        <v>933</v>
-      </c>
-      <c r="O26" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P26" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q26" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="19">
-        <v>0</v>
-      </c>
-      <c r="X26" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="2"/>
-      <c r="AA26" s="2"/>
-      <c r="AB26" s="2"/>
-      <c r="AC26" s="2"/>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A27" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="5"/>
-      <c r="K27" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L27" s="1"/>
-      <c r="M27" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N27" s="2">
-        <v>4936</v>
-      </c>
-      <c r="O27" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P27" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q27" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="19">
-        <v>0</v>
-      </c>
-      <c r="X27" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="2"/>
-      <c r="AA27" s="2"/>
-      <c r="AB27" s="2"/>
-      <c r="AC27" s="2"/>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J28" s="5"/>
-      <c r="K28" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L28" s="1"/>
-      <c r="M28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N28" s="2">
-        <v>5356</v>
-      </c>
-      <c r="O28" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P28" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q28" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="19">
-        <v>0</v>
-      </c>
-      <c r="X28" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="2"/>
-      <c r="AA28" s="2"/>
-      <c r="AB28" s="2"/>
-      <c r="AC28" s="2"/>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A29" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="5"/>
-      <c r="K29" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L29" s="1"/>
-      <c r="M29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N29" s="2">
-        <v>6758</v>
-      </c>
-      <c r="O29" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P29" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q29" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U29" s="2"/>
-      <c r="V29" s="2"/>
-      <c r="W29" s="19">
-        <v>0</v>
-      </c>
-      <c r="X29" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="2"/>
-      <c r="AA29" s="2"/>
-      <c r="AB29" s="2"/>
-      <c r="AC29" s="2"/>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A30" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J30" s="5"/>
-      <c r="K30" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L30" s="1"/>
-      <c r="M30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N30" s="2">
-        <v>4871</v>
-      </c>
-      <c r="O30" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P30" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q30" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U30" s="2"/>
-      <c r="V30" s="2"/>
-      <c r="W30" s="19">
-        <v>0</v>
-      </c>
-      <c r="X30" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="2"/>
-      <c r="AA30" s="2"/>
-      <c r="AB30" s="2"/>
-      <c r="AC30" s="2"/>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A31" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J31" s="5"/>
-      <c r="K31" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L31" s="1"/>
-      <c r="M31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6387</v>
-      </c>
-      <c r="O31" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P31" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q31" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S31" s="2"/>
-      <c r="T31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U31" s="2"/>
-      <c r="V31" s="2"/>
-      <c r="W31" s="19">
-        <v>0</v>
-      </c>
-      <c r="X31" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="2"/>
-      <c r="AA31" s="2"/>
-      <c r="AB31" s="2"/>
-      <c r="AC31" s="2"/>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="5"/>
-      <c r="K32" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L32" s="1"/>
-      <c r="M32" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N32" s="2">
-        <v>6758</v>
-      </c>
-      <c r="O32" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P32" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q32" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R32" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="19">
-        <v>0</v>
-      </c>
-      <c r="X32" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="2"/>
-      <c r="AA32" s="2"/>
-      <c r="AB32" s="2"/>
-      <c r="AC32" s="2"/>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A33" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="5"/>
-      <c r="K33" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L33" s="1"/>
-      <c r="M33" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N33" s="2">
-        <v>6918</v>
-      </c>
-      <c r="O33" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P33" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q33" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R33" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S33" s="2"/>
-      <c r="T33" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="19">
-        <v>0</v>
-      </c>
-      <c r="X33" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="2"/>
-      <c r="AA33" s="2"/>
-      <c r="AB33" s="2"/>
-      <c r="AC33" s="2"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A34" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L34" s="1"/>
-      <c r="M34" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N34" s="2">
-        <v>3944</v>
-      </c>
-      <c r="O34" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P34" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q34" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U34" s="2"/>
-      <c r="V34" s="2"/>
-      <c r="W34" s="19">
-        <v>0</v>
-      </c>
-      <c r="X34" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="2"/>
-      <c r="AA34" s="2"/>
-      <c r="AB34" s="2"/>
-      <c r="AC34" s="2"/>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A35" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="5"/>
-      <c r="K35" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L35" s="1"/>
-      <c r="M35" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N35" s="2">
-        <v>7133</v>
-      </c>
-      <c r="O35" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P35" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q35" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S35" s="2"/>
-      <c r="T35" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U35" s="2"/>
-      <c r="V35" s="2"/>
-      <c r="W35" s="19">
-        <v>0</v>
-      </c>
-      <c r="X35" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="2"/>
-      <c r="AA35" s="2"/>
-      <c r="AB35" s="2"/>
-      <c r="AC35" s="2"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A36" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J36" s="5"/>
-      <c r="K36" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L36" s="1"/>
-      <c r="M36" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N36" s="2">
-        <v>9084</v>
-      </c>
-      <c r="O36" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P36" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q36" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S36" s="2"/>
-      <c r="T36" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U36" s="2"/>
-      <c r="V36" s="2"/>
-      <c r="W36" s="19">
-        <v>0</v>
-      </c>
-      <c r="X36" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="2"/>
-      <c r="AA36" s="2"/>
-      <c r="AB36" s="2"/>
-      <c r="AC36" s="2"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A37" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J37" s="5"/>
-      <c r="K37" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L37" s="1"/>
-      <c r="M37" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O37" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="P37" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q37" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S37" s="2"/>
-      <c r="T37" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U37" s="2"/>
-      <c r="V37" s="2"/>
-      <c r="W37" s="19">
-        <v>0</v>
-      </c>
-      <c r="X37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="2"/>
-      <c r="AA37" s="2"/>
-      <c r="AB37" s="2"/>
-      <c r="AC37" s="2"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R37">
-    <sortCondition ref="G2:G37"/>
-    <sortCondition ref="J2:J37"/>
-    <sortCondition ref="K2:K37"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R21">
+    <sortCondition ref="G2:G21"/>
+    <sortCondition ref="J2:J21"/>
+    <sortCondition ref="K2:K21"/>
   </sortState>
-  <conditionalFormatting sqref="Q38:Q1048576">
-    <cfRule type="colorScale" priority="125">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22:G35 G2:G20">
-    <cfRule type="containsText" dxfId="3" priority="43" operator="containsText" text="excluded">
+  <conditionalFormatting sqref="G2:G20">
+    <cfRule type="containsText" dxfId="1" priority="43" operator="containsText" text="excluded">
       <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21">
-    <cfRule type="containsText" dxfId="2" priority="24" operator="containsText" text="excluded">
+    <cfRule type="containsText" dxfId="0" priority="24" operator="containsText" text="excluded">
       <formula>NOT(ISERROR(SEARCH("excluded",G21)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G36">
-    <cfRule type="containsText" dxfId="1" priority="21" operator="containsText" text="excluded">
-      <formula>NOT(ISERROR(SEARCH("excluded",G36)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G37">
-    <cfRule type="containsText" dxfId="0" priority="20" operator="containsText" text="excluded">
-      <formula>NOT(ISERROR(SEARCH("excluded",G37)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
@@ -4312,8 +3026,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M37">
-    <cfRule type="colorScale" priority="148">
+  <conditionalFormatting sqref="Q22:Q1048576">
+    <cfRule type="colorScale" priority="149">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O21">
+    <cfRule type="colorScale" priority="151">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4324,8 +3050,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O37">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="P2:P21">
+    <cfRule type="colorScale" priority="152">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4336,8 +3062,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P37">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="Q2:Q21">
+    <cfRule type="colorScale" priority="153">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4348,8 +3074,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q37">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="X2:X21">
+    <cfRule type="colorScale" priority="154">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4360,8 +3086,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X37">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="Y2:Y21">
+    <cfRule type="colorScale" priority="155">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4372,20 +3098,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y37">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W37">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="W2:W21">
+    <cfRule type="colorScale" priority="156">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/tabular/reference/ervr/ervr_data.xlsx
+++ b/tabular/reference/ervr/ervr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2EF283-6AB4-E54E-8A84-8CCA826B6C85}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440E3D00-145D-D540-A5FD-E0AB5DE56928}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="2800" windowWidth="25980" windowHeight="14960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="5260" windowWidth="27860" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="113">
   <si>
     <t>sequenceID</t>
   </si>
@@ -191,9 +191,6 @@
     <t>ERV-1.Zeta</t>
   </si>
   <si>
-    <t>ERV-1.Theta</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta.HF</t>
   </si>
   <si>
@@ -360,6 +357,18 @@
   </si>
   <si>
     <t>ERVR-1.Zeta.84</t>
+  </si>
+  <si>
+    <t>MER-110</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.24.110</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 110</t>
+  </si>
+  <si>
+    <t>ERV-1.Theta.24</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1007,17 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1336,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1364,31 +1383,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>50</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I1" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>75</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>76</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>26</v>
@@ -1397,19 +1416,19 @@
         <v>27</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N1" s="15" t="s">
         <v>1</v>
       </c>
       <c r="O1" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>78</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>79</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>28</v>
@@ -1418,22 +1437,22 @@
         <v>29</v>
       </c>
       <c r="T1" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="U1" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="V1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="X1" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="Y1" s="15" t="s">
         <v>84</v>
-      </c>
-      <c r="Y1" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="Z1" s="4" t="s">
         <v>30</v>
@@ -1442,10 +1461,10 @@
         <v>31</v>
       </c>
       <c r="AB1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC1" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.2">
@@ -1453,7 +1472,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>17</v>
@@ -1462,16 +1481,16 @@
         <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>3</v>
@@ -1488,20 +1507,20 @@
         <v>6639</v>
       </c>
       <c r="O2" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="Q2" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q2" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S2" s="2"/>
       <c r="T2" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
@@ -1521,70 +1540,46 @@
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>3</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="K3" s="2"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" s="2">
-        <v>7048</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="P3" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q3" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
-      <c r="T3" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
-      <c r="W3" s="17">
-        <v>0</v>
-      </c>
-      <c r="X3" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="17">
-        <v>0</v>
-      </c>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
       <c r="AB3" s="2"/>
@@ -1592,28 +1587,28 @@
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>3</v>
@@ -1627,23 +1622,23 @@
         <v>1</v>
       </c>
       <c r="N4" s="2">
-        <v>8120</v>
+        <v>7048</v>
       </c>
       <c r="O4" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P4" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P4" s="17" t="s">
+      <c r="Q4" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q4" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S4" s="2"/>
       <c r="T4" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
@@ -1663,60 +1658,58 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>95</v>
+        <v>15</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>58</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="L5" s="1"/>
       <c r="M5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N5" s="2">
-        <v>4981</v>
+        <v>8120</v>
       </c>
       <c r="O5" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P5" s="17" t="s">
+      <c r="Q5" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S5" s="2"/>
       <c r="T5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
@@ -1734,30 +1727,30 @@
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
     </row>
-    <row r="6" spans="1:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>3</v>
@@ -1767,29 +1760,29 @@
         <v>19</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N6" s="2">
-        <v>4798</v>
+        <v>4981</v>
       </c>
       <c r="O6" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P6" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P6" s="17" t="s">
+      <c r="Q6" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q6" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S6" s="2"/>
       <c r="T6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
@@ -1807,30 +1800,30 @@
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>3</v>
@@ -1846,23 +1839,23 @@
         <v>1</v>
       </c>
       <c r="N7" s="2">
-        <v>6996</v>
+        <v>4798</v>
       </c>
       <c r="O7" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P7" s="17" t="s">
+      <c r="Q7" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q7" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="2"/>
       <c r="T7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
@@ -1882,28 +1875,28 @@
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>3</v>
@@ -1912,28 +1905,30 @@
       <c r="K8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="M8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N8" s="2">
-        <v>5586</v>
+        <v>6996</v>
       </c>
       <c r="O8" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P8" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P8" s="17" t="s">
+      <c r="Q8" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S8" s="2"/>
       <c r="T8" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
@@ -1953,22 +1948,22 @@
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>51</v>
@@ -1988,23 +1983,23 @@
         <v>1</v>
       </c>
       <c r="N9" s="2">
-        <v>4285</v>
+        <v>5586</v>
       </c>
       <c r="O9" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P9" s="17" t="s">
+      <c r="Q9" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q9" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S9" s="2"/>
       <c r="T9" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
@@ -2024,22 +2019,22 @@
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>51</v>
@@ -2059,23 +2054,23 @@
         <v>1</v>
       </c>
       <c r="N10" s="2">
-        <v>4880</v>
+        <v>4285</v>
       </c>
       <c r="O10" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P10" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P10" s="17" t="s">
+      <c r="Q10" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q10" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S10" s="2"/>
       <c r="T10" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
@@ -2095,22 +2090,22 @@
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>51</v>
@@ -2130,23 +2125,23 @@
         <v>1</v>
       </c>
       <c r="N11" s="2">
-        <v>2880</v>
+        <v>4880</v>
       </c>
       <c r="O11" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P11" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P11" s="17" t="s">
+      <c r="Q11" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q11" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S11" s="2"/>
       <c r="T11" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
@@ -2166,60 +2161,58 @@
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>97</v>
+        <v>25</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>92</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J12" s="5"/>
       <c r="K12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" s="8"/>
+        <v>19</v>
+      </c>
+      <c r="L12" s="1"/>
       <c r="M12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N12" s="2">
-        <v>6070</v>
+        <v>2880</v>
       </c>
       <c r="O12" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P12" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P12" s="17" t="s">
+      <c r="Q12" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q12" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S12" s="2"/>
       <c r="T12" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
@@ -2239,22 +2232,22 @@
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>51</v>
@@ -2266,33 +2259,33 @@
         <v>4</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L13" s="9"/>
+      <c r="L13" s="8"/>
       <c r="M13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N13" s="2">
-        <v>4996</v>
+        <v>6070</v>
       </c>
       <c r="O13" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P13" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P13" s="17" t="s">
+      <c r="Q13" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q13" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S13" s="2"/>
       <c r="T13" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
@@ -2312,22 +2305,22 @@
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>51</v>
@@ -2339,33 +2332,33 @@
         <v>4</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="1"/>
+      <c r="L14" s="9"/>
       <c r="M14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N14" s="2">
-        <v>5530</v>
+        <v>4996</v>
       </c>
       <c r="O14" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P14" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P14" s="17" t="s">
+      <c r="Q14" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q14" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S14" s="2"/>
       <c r="T14" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
@@ -2385,22 +2378,22 @@
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>51</v>
@@ -2412,7 +2405,7 @@
         <v>4</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>5</v>
@@ -2422,23 +2415,23 @@
         <v>1</v>
       </c>
       <c r="N15" s="2">
-        <v>3556</v>
+        <v>5530</v>
       </c>
       <c r="O15" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P15" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P15" s="17" t="s">
+      <c r="Q15" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q15" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S15" s="2"/>
       <c r="T15" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
@@ -2458,22 +2451,22 @@
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>51</v>
@@ -2485,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>5</v>
@@ -2495,23 +2488,23 @@
         <v>1</v>
       </c>
       <c r="N16" s="2">
-        <v>3329</v>
+        <v>3556</v>
       </c>
       <c r="O16" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P16" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P16" s="17" t="s">
+      <c r="Q16" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q16" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S16" s="2"/>
       <c r="T16" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
@@ -2531,22 +2524,22 @@
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>51</v>
@@ -2558,7 +2551,7 @@
         <v>4</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>5</v>
@@ -2568,23 +2561,23 @@
         <v>1</v>
       </c>
       <c r="N17" s="2">
-        <v>5685</v>
+        <v>3329</v>
       </c>
       <c r="O17" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P17" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P17" s="17" t="s">
+      <c r="Q17" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q17" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S17" s="2"/>
       <c r="T17" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
@@ -2604,22 +2597,22 @@
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>51</v>
@@ -2631,7 +2624,7 @@
         <v>4</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>5</v>
@@ -2641,23 +2634,23 @@
         <v>1</v>
       </c>
       <c r="N18" s="2">
-        <v>5023</v>
+        <v>5685</v>
       </c>
       <c r="O18" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P18" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P18" s="17" t="s">
+      <c r="Q18" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q18" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S18" s="2"/>
       <c r="T18" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
@@ -2677,22 +2670,22 @@
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>51</v>
@@ -2704,7 +2697,7 @@
         <v>4</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>5</v>
@@ -2714,23 +2707,23 @@
         <v>1</v>
       </c>
       <c r="N19" s="2">
-        <v>6189</v>
+        <v>5023</v>
       </c>
       <c r="O19" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P19" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P19" s="17" t="s">
+      <c r="Q19" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q19" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
@@ -2750,60 +2743,60 @@
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>103</v>
+        <v>13</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="10" t="s">
-        <v>66</v>
+      <c r="H20" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="2" t="b">
         <v>1</v>
       </c>
       <c r="N20" s="2">
-        <v>5343</v>
+        <v>6189</v>
       </c>
       <c r="O20" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P20" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P20" s="17" t="s">
+      <c r="Q20" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q20" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S20" s="2"/>
       <c r="T20" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
@@ -2823,56 +2816,60 @@
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>70</v>
+      <c r="H21" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>4</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>67</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="L21" s="1"/>
       <c r="M21" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="N21" s="2">
+        <v>5343</v>
+      </c>
       <c r="O21" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P21" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P21" s="17" t="s">
+      <c r="Q21" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="Q21" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>2</v>
       </c>
       <c r="S21" s="2"/>
       <c r="T21" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
@@ -2890,23 +2887,104 @@
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
     </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="P22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q22" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="17">
+        <v>0</v>
+      </c>
+      <c r="X22" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2"/>
+      <c r="AC22" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R21">
-    <sortCondition ref="G2:G21"/>
-    <sortCondition ref="J2:J21"/>
-    <sortCondition ref="K2:K21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R22">
+    <sortCondition ref="G2:G22"/>
+    <sortCondition ref="J2:J22"/>
+    <sortCondition ref="K2:K22"/>
   </sortState>
-  <conditionalFormatting sqref="G2:G20">
-    <cfRule type="containsText" dxfId="1" priority="43" operator="containsText" text="excluded">
+  <conditionalFormatting sqref="G2 G4:G21">
+    <cfRule type="containsText" dxfId="2" priority="44" operator="containsText" text="excluded">
       <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G21">
-    <cfRule type="containsText" dxfId="0" priority="24" operator="containsText" text="excluded">
-      <formula>NOT(ISERROR(SEARCH("excluded",G21)))</formula>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="containsText" dxfId="1" priority="25" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -2918,7 +2996,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1">
+  <conditionalFormatting sqref="Q1">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -2930,7 +3008,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1">
+  <conditionalFormatting sqref="T1">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -2942,7 +3020,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T1">
+  <conditionalFormatting sqref="U1">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -2954,7 +3032,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U1">
+  <conditionalFormatting sqref="V1">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -2966,7 +3044,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V1">
+  <conditionalFormatting sqref="AB1:AC1">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W1:Y1">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -2978,32 +3068,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB1:AC1">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W1:Y1">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="colorScale" priority="147">
+    <cfRule type="colorScale" priority="148">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3015,7 +3081,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3026,8 +3092,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q22:Q1048576">
-    <cfRule type="colorScale" priority="149">
+  <conditionalFormatting sqref="Q23:Q1048576">
+    <cfRule type="colorScale" priority="150">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3038,19 +3104,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
-    <cfRule type="colorScale" priority="151">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="O2:O22">
     <cfRule type="colorScale" priority="152">
       <colorScale>
         <cfvo type="min"/>
@@ -3062,7 +3116,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="P2:P22">
     <cfRule type="colorScale" priority="153">
       <colorScale>
         <cfvo type="min"/>
@@ -3074,7 +3128,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X21">
+  <conditionalFormatting sqref="Q2:Q22">
     <cfRule type="colorScale" priority="154">
       <colorScale>
         <cfvo type="min"/>
@@ -3086,7 +3140,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y21">
+  <conditionalFormatting sqref="X2:X22">
     <cfRule type="colorScale" priority="155">
       <colorScale>
         <cfvo type="min"/>
@@ -3098,7 +3152,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W21">
+  <conditionalFormatting sqref="Y2:Y22">
     <cfRule type="colorScale" priority="156">
       <colorScale>
         <cfvo type="min"/>
@@ -3110,6 +3164,23 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W22">
+    <cfRule type="colorScale" priority="157">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/tabular/reference/ervr/ervr_data.xlsx
+++ b/tabular/reference/ervr/ervr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440E3D00-145D-D540-A5FD-E0AB5DE56928}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126249C9-5552-5D47-8374-1FE771EEA27B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="5260" windowWidth="27860" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="940" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="2" r:id="rId1"/>

--- a/tabular/reference/ervr/ervr_data.xlsx
+++ b/tabular/reference/ervr/ervr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126249C9-5552-5D47-8374-1FE771EEA27B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFAA139-C061-3045-A2EE-DBEF080874F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="1640" windowWidth="27860" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="2" r:id="rId1"/>

--- a/tabular/reference/ervr/ervr_data.xlsx
+++ b/tabular/reference/ervr/ervr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFAA139-C061-3045-A2EE-DBEF080874F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F2839C-A32E-2B4C-B5A1-EAD19974C958}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="1640" windowWidth="27860" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="6900" windowWidth="27860" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="2" r:id="rId1"/>

--- a/tabular/reference/ervr/ervr_data.xlsx
+++ b/tabular/reference/ervr/ervr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F2839C-A32E-2B4C-B5A1-EAD19974C958}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244988D6-F325-DF43-A569-93B9CC4B2461}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="6900" windowWidth="27860" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="940" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="2" r:id="rId1"/>
